--- a/artfynd/A 41443-2024 artfynd.xlsx
+++ b/artfynd/A 41443-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120492974</v>
+        <v>120493287</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656009</v>
+        <v>655981</v>
       </c>
       <c r="R2" t="n">
-        <v>6680362</v>
+        <v>6680210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120493287</v>
+        <v>120492974</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655981</v>
+        <v>656009</v>
       </c>
       <c r="R3" t="n">
-        <v>6680210</v>
+        <v>6680362</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41443-2024 artfynd.xlsx
+++ b/artfynd/A 41443-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120493287</v>
+        <v>120492238</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655981</v>
+        <v>656118</v>
       </c>
       <c r="R2" t="n">
-        <v>6680210</v>
+        <v>6680343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120492974</v>
+        <v>120493224</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656009</v>
+        <v>656026</v>
       </c>
       <c r="R3" t="n">
-        <v>6680362</v>
+        <v>6680222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120493224</v>
+        <v>120494880</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656026</v>
+        <v>656128</v>
       </c>
       <c r="R4" t="n">
-        <v>6680222</v>
+        <v>6680242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120494880</v>
+        <v>120492109</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>91200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656128</v>
+        <v>656152</v>
       </c>
       <c r="R5" t="n">
-        <v>6680242</v>
+        <v>6680290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,6 +1107,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1367,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120492238</v>
+        <v>120493287</v>
       </c>
       <c r="B8" t="n">
         <v>100194</v>
@@ -1407,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656118</v>
+        <v>655981</v>
       </c>
       <c r="R8" t="n">
-        <v>6680343</v>
+        <v>6680210</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120492109</v>
+        <v>120492974</v>
       </c>
       <c r="B9" t="n">
-        <v>91200</v>
+        <v>100194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656152</v>
+        <v>656009</v>
       </c>
       <c r="R9" t="n">
-        <v>6680290</v>
+        <v>6680362</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,21 +1590,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 41443-2024 artfynd.xlsx
+++ b/artfynd/A 41443-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120492238</v>
+        <v>120492974</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656118</v>
+        <v>656009</v>
       </c>
       <c r="R2" t="n">
-        <v>6680343</v>
+        <v>6680362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120494880</v>
+        <v>120493287</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656128</v>
+        <v>655981</v>
       </c>
       <c r="R4" t="n">
-        <v>6680242</v>
+        <v>6680210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120492109</v>
+        <v>120492238</v>
       </c>
       <c r="B5" t="n">
-        <v>91200</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656152</v>
+        <v>656118</v>
       </c>
       <c r="R5" t="n">
-        <v>6680290</v>
+        <v>6680343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,21 +1107,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120493444</v>
+        <v>120493072</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1135,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smörkyeröret, Smörkyeröret, Upl</t>
+          <t>Skogen NV Haglösa ängar, Film, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655976</v>
+        <v>656003</v>
       </c>
       <c r="R6" t="n">
-        <v>6680147</v>
+        <v>6680254</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,6 +1224,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120493072</v>
+        <v>120494880</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,43 +1267,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogen NV Haglösa ängar, Film, Upl</t>
+          <t>Skogen NV Haglösa ängar, Skogen NV Haglösa ängar, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656003</v>
+        <v>656128</v>
       </c>
       <c r="R7" t="n">
-        <v>6680254</v>
+        <v>6680242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,21 +1351,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120493287</v>
+        <v>120492109</v>
       </c>
       <c r="B8" t="n">
-        <v>100194</v>
+        <v>91200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655981</v>
+        <v>656152</v>
       </c>
       <c r="R8" t="n">
-        <v>6680210</v>
+        <v>6680290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,6 +1463,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120492974</v>
+        <v>120493444</v>
       </c>
       <c r="B9" t="n">
         <v>100194</v>
@@ -1530,14 +1530,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skogen NV Haglösa ängar, Skogen NV Haglösa ängar, Upl</t>
+          <t>Smörkyeröret, Smörkyeröret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656009</v>
+        <v>655976</v>
       </c>
       <c r="R9" t="n">
-        <v>6680362</v>
+        <v>6680147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
